--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1075952-9-CM25</t>
+          <t>709603-64-SE25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,28 +554,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34413.46</v>
+        <v>54155.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>612-227-CM25</t>
+          <t>1075952-9-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +594,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,28 +619,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>299008.95</v>
+        <v>34413.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2083-2-CM25</t>
+          <t>612-227-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -656,17 +664,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +699,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30268.75</v>
+        <v>299008.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2404-528-CM25</t>
+          <t>2083-2-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,32 +725,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>33804.35</v>
+        <v>30268.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1093219-4-CM25</t>
+          <t>2404-528-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,37 +781,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SONDA S A</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83.628.100-4</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39262.17</v>
+        <v>33804.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233623-153-CM25</t>
+          <t>1093219-4-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -844,27 +852,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>SONDA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>83.628.100-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +882,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>383543.33</v>
+        <v>39262.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2153-243-CM25</t>
+          <t>1233623-153-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +903,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,43 +913,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.608.503-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hospital Sanatorio San José de Maipo</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>606765.79</v>
+        <v>383543.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1177296-144-CM25</t>
+          <t>1151575-33-SE25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,53 +968,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>65.195.573-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Nueva Gestión</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.325.497-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>54465.04</v>
+        <v>8076.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1214102-884-CM25</t>
+          <t>1177296-144-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1033,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,28 +1058,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PAIS DIGITAL SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.015.597-5</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>50479.69</v>
+        <v>54465.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1016-27-CM25</t>
+          <t>2153-243-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1098,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.608.503-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Hospital Sanatorio San José de Maipo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1123,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y SISTEMAS DE INFORMACION LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.291.521-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1138,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>31841.15</v>
+        <v>606765.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>885-321-CM25</t>
+          <t>1214102-884-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1159,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1169,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1184,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>PAIS DIGITAL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.015.597-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>73766.77</v>
+        <v>50479.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>730566-177-CM25</t>
+          <t>885-321-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1229,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1249,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1264,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>39665.75</v>
+        <v>73766.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1605-111-CM25</t>
+          <t>730566-177-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1285,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1295,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,28 +1310,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>184253.25</v>
+        <v>39665.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2307-2925-CM25</t>
+          <t>1016-27-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1350,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,27 +1360,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>CONSULTORIA Y SISTEMAS DE INFORMACION LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.291.521-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1390,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>167401.82</v>
+        <v>31841.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3598-430-CM25</t>
+          <t>2036-255-SE25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,53 +1411,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>61.602.247-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23779.96</v>
+        <v>14113.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1588-31-CM25</t>
+          <t>1605-111-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1476,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1486,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1501,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1516,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32671.79</v>
+        <v>184253.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45-103-CM25</t>
+          <t>2307-2925-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,37 +1537,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1577,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>122490.05</v>
+        <v>167401.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>924-71-CM25</t>
+          <t>3598-430-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,48 +1603,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>22556.04</v>
+        <v>23779.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>603663-159-CM25</t>
+          <t>924-71-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,12 +1673,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1688,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7727.29</v>
+        <v>22556.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>757-247-CM25</t>
+          <t>603663-159-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1728,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1738,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1753,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11713.2</v>
+        <v>7727.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1016414-59-CM25</t>
+          <t>45-103-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1793,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1803,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1818,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1833,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12924.91</v>
+        <v>122490.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1725-4779-CM25</t>
+          <t>1588-31-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1854,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,17 +1864,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1843,20 +1887,24 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>43194.23</v>
+        <v>32671.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1725-4780-CM25</t>
+          <t>711841-237-SE25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1919,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,43 +1929,47 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>77.240.269-4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>16727.54</v>
+        <v>23687.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2268-106-CM25</t>
+          <t>1016414-59-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1984,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2009,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>236229.85</v>
+        <v>12924.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4704-242-CM25</t>
+          <t>757-247-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +2049,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.073.000-6</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL MONTE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2074,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2089,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18864.37</v>
+        <v>11713.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1725-4774-CM25</t>
+          <t>1725-4779-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2110,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,28 +2135,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ABENIS</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.217.169-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>19368.28</v>
+        <v>43194.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2277-40-CM25</t>
+          <t>1725-4780-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,37 +2175,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.240.269-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2215,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>146701.68</v>
+        <v>16727.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1080089-384-CM25</t>
+          <t>2268-106-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2236,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,43 +2246,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14515.89</v>
+        <v>236229.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3553-214-CM25</t>
+          <t>4704-242-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2301,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.073.000-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE EL MONTE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,28 +2326,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>38368.32</v>
+        <v>18864.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1385462-57-CM25</t>
+          <t>1725-4774-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2366,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,43 +2376,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>ABENIS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.217.169-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10558.92</v>
+        <v>19368.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2279-370-CM25</t>
+          <t>2277-40-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2431,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2456,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2471,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>63214.01</v>
+        <v>146701.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1607-93-CM25</t>
+          <t>1080089-384-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,37 +2492,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2532,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>705074.45</v>
+        <v>14515.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>587-197-CM25</t>
+          <t>1385462-57-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2553,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2563,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2578,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ENVISION INVERSIONES LIMITADA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.693.295-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>21169.75</v>
+        <v>10558.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057414-203-CM25</t>
+          <t>3553-214-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2618,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,27 +2628,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2658,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18269.1</v>
+        <v>38368.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1005498-142-CM25</t>
+          <t>1607-93-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2679,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2689,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2704,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS GOVMS SPA</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.384.526-5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>21288.46</v>
+        <v>705074.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2282-94-CM25</t>
+          <t>2279-370-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2744,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2754,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>67034.67999999999</v>
+        <v>63214.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1725-4837-CM25</t>
+          <t>587-197-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2809,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2819,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TIMIX SERVICE SPA</t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.285.037-9</t>
+          <t>76.693.295-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2849,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>43293.68</v>
+        <v>21169.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1121-42-CM25</t>
+          <t>1057414-203-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2870,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,43 +2880,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>31329.9</v>
+        <v>18269.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1704-2933-CM25</t>
+          <t>1005498-142-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2935,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,43 +2945,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>SERVICIOS INFORMATICOS GOVMS SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.384.526-5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>40467.49</v>
+        <v>21288.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1314-3-CM25</t>
+          <t>2282-94-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +3000,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,97 +3010,418 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>51260.51</v>
+        <v>67034.67999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>1725-4837-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TIMIX SERVICE SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.285.037-9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>43293.68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1057547-23023-SE25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>47002.28</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1314-3-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.706.000-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>51260.51</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1121-42-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.706.000-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>KUANTUM SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.553.335-K</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>31329.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1704-2933-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Kibernum S.A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>40467.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>1704-2935-CM25</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>may-2025</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>61.606.608-0</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Kibernum S.A</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>40467.49</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2025.xlsx
@@ -3354,7 +3354,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3415,7 +3419,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
